--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-10-2025.xlsx
@@ -1415,7 +1415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£24.01</t>
+          <t>£23.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£26.02</t>
+          <t>£25.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.68</t>
+          <t>£25.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
